--- a/business_forms/039_spec_creation--business_forms.xlsx
+++ b/business_forms/039_spec_creation--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>updated_by</t>
+          <t>updated_by_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Updated By</t>
+          <t>Updated By 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>spec_status</t>
+          <t>spec_status_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spec Status</t>
+          <t>Spec Status 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>spec_description</t>
+          <t>spec_description_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spec Description</t>
+          <t>Spec Description 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>spec_name</t>
+          <t>spec_name_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spec Name</t>
+          <t>Spec Name 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>assigned_by</t>
+          <t>assigned_by_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Assigned By</t>
+          <t>Assigned By 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>created_at_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Created At</t>
+          <t>Created At 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,9 +1101,9 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'service',_'value':_'service'}</t>
+          <t>service</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Service', 'value': 'service'}</t>
+          <t>Service</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'product',_'value':_'product'}</t>
+          <t>product</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Product', 'value': 'product'}</t>
+          <t>Product</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'in_progress',_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'In Progress', 'value': 'in_progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'complete',_'value':_'complete'}</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Complete', 'value': 'complete'}</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'cancelled',_'value':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Cancelled', 'value': 'cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'john_doe',_'value':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'John Doe', 'value': 'john_doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1233,63 +1233,63 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'jane_doe',_'value':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Jane Doe', 'value': 'jane_doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>spec_status_choices</t>
+          <t>spec_status_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'in_progress',_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'In Progress', 'value': 'in_progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>spec_status_choices</t>
+          <t>spec_status_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'complete',_'value':_'complete'}</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Complete', 'value': 'complete'}</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>spec_status_choices</t>
+          <t>spec_status_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'cancelled',_'value':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Cancelled', 'value': 'cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
